--- a/FabricaHilos/Data/Sistemas/Indicadores/1. Sistemas - (OR) Indicador_Desarrollo.xlsx
+++ b/FabricaHilos/Data/Sistemas/Indicadores/1. Sistemas - (OR) Indicador_Desarrollo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CP710_03\LA COLONIAL Dropbox\Control Calidad La Colonial\SGC LA COLONIAL FABRICA DE HILOS\00. PROPUESTA\1. ISO 9001\4. Indicadores\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Development\Code\WorkSpace\FabricaHilosRepository\FabricaHilos\Data\Sistemas\Indicadores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B457B138-8F96-4AA3-9EDE-25A7E0591EB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFCE8D1C-ACB9-4C3A-92FA-49C6B915EEBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="767" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -315,9 +315,6 @@
     <t>DIC</t>
   </si>
   <si>
-    <t>TRIMESTRE</t>
-  </si>
-  <si>
     <t>VERIFICACIÓN DE CUMPLIMIENTO</t>
   </si>
   <si>
@@ -327,9 +324,6 @@
     <t>≥</t>
   </si>
   <si>
-    <t>SISTEMAS</t>
-  </si>
-  <si>
     <t>María Astete</t>
   </si>
   <si>
@@ -343,6 +337,12 @@
   </si>
   <si>
     <t>Es el porcentaje de solicitudes atendidas sobre el total de solicitudes recibidas</t>
+  </si>
+  <si>
+    <t>REDUCIR LAS COLAS DE ATENCION (DESARROLLO)</t>
+  </si>
+  <si>
+    <t>SEMESTRAL</t>
   </si>
 </sst>
 </file>
@@ -1308,587 +1308,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="es-ES"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="8.8714317474191381E-2"/>
-          <c:y val="2.9616588246834167E-2"/>
-          <c:w val="0.88633409880516434"/>
-          <c:h val="0.88790115867684516"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:v>Nivel de cumplimiento</c:v>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="C5C000"/>
-            </a:solidFill>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>ENE!$D$21:$O$21</c:f>
-              <c:strCache>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>ENE</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>FEB</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>MAR</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>ABR</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>MAY</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>JUN</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>JUL</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>AGO</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>SET</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>OCT</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>NOV</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>DIC</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>ENE!$D$24:$O$24</c:f>
-              <c:numCache>
-                <c:formatCode>0.0%</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D9C5-42BA-BFD6-62B6A3688E8B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="150"/>
-        <c:axId val="87269376"/>
-        <c:axId val="87270912"/>
-      </c:barChart>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>ENE!$B$25</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>META</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln>
-              <a:solidFill>
-                <a:schemeClr val="tx2"/>
-              </a:solidFill>
-            </a:ln>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>ENE!$D$21:$O$21</c:f>
-              <c:strCache>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>ENE</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>FEB</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>MAR</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>ABR</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>MAY</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>JUN</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>JUL</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>AGO</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>SET</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>OCT</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>NOV</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>DIC</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>ENE!$D$25:$O$25</c:f>
-              <c:numCache>
-                <c:formatCode>0%</c:formatCode>
-                <c:ptCount val="12"/>
-                <c:pt idx="0">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>0.9</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>0.9</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D9C5-42BA-BFD6-62B6A3688E8B}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="87269376"/>
-        <c:axId val="87270912"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="87269376"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="5000"/>
-                  <a:lumOff val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:minorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="87270912"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="87270912"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="1"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:minorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="5000"/>
-                  <a:lumOff val="95000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:minorGridlines>
-        <c:numFmt formatCode="0%" sourceLinked="0"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="es-PE"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="87269376"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-        <c:minorUnit val="1.0000000000000002E-2"/>
-      </c:valAx>
-      <c:spPr>
-        <a:solidFill>
-          <a:schemeClr val="bg1"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="t"/>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.80316457025949373"/>
-          <c:y val="0.57577722460502889"/>
-          <c:w val="0.19683542426947229"/>
-          <c:h val="7.4162198236304253E-2"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="es-PE"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:gradFill flip="none" rotWithShape="1">
-      <a:gsLst>
-        <a:gs pos="100000">
-          <a:schemeClr val="bg1">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
-        </a:gs>
-        <a:gs pos="86000">
-          <a:schemeClr val="bg1"/>
-        </a:gs>
-      </a:gsLst>
-      <a:path path="rect">
-        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-      </a:path>
-      <a:tileRect/>
-    </a:gradFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-    <a:scene3d>
-      <a:camera prst="orthographicFront"/>
-      <a:lightRig rig="threePt" dir="t"/>
-    </a:scene3d>
-    <a:sp3d>
-      <a:bevelT w="190500" h="38100"/>
-    </a:sp3d>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="es-PE"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup orientation="portrait"/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -1941,44 +1360,6 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>334240</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>180976</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>1468581</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>1133475</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Gráfico 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
@@ -1987,8 +1368,8 @@
       <xdr:rowOff>66675</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="5109784" cy="409023"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="CuadroTexto 5">
@@ -2166,7 +1547,7 @@
           </xdr:txBody>
         </xdr:sp>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="6" name="CuadroTexto 5">
@@ -2819,7 +2200,7 @@
       <c r="C8" s="107"/>
       <c r="D8" s="108"/>
       <c r="E8" s="109" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F8" s="109"/>
       <c r="G8" s="109"/>
@@ -2893,7 +2274,7 @@
       <c r="C10" s="87"/>
       <c r="D10" s="88"/>
       <c r="E10" s="89" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F10" s="89"/>
       <c r="G10" s="89"/>
@@ -2903,7 +2284,7 @@
       <c r="K10" s="89"/>
       <c r="L10" s="89"/>
       <c r="M10" s="90" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N10" s="90"/>
       <c r="O10" s="91">
@@ -2965,7 +2346,7 @@
       <c r="C12" s="125"/>
       <c r="D12" s="125"/>
       <c r="E12" s="99" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F12" s="99"/>
       <c r="G12" s="99"/>
@@ -2975,17 +2356,17 @@
       </c>
       <c r="J12" s="90"/>
       <c r="K12" s="50" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L12" s="51">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="M12" s="90" t="s">
         <v>8</v>
       </c>
       <c r="N12" s="90"/>
       <c r="O12" s="99" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="P12" s="99"/>
       <c r="Q12" s="2"/>
@@ -3043,7 +2424,7 @@
       <c r="C14" s="100"/>
       <c r="D14" s="100"/>
       <c r="E14" s="101" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F14" s="102"/>
       <c r="G14" s="102"/>
@@ -3119,7 +2500,7 @@
       <c r="F16" s="132"/>
       <c r="G16" s="43">
         <f>L12</f>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H16" s="44"/>
       <c r="I16" s="45"/>
@@ -3129,7 +2510,7 @@
       <c r="M16" s="47"/>
       <c r="N16" s="48">
         <f>L12</f>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="O16" s="133" t="s">
         <v>22</v>
@@ -3378,7 +2759,7 @@
     <row r="24" spans="1:31" s="3" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4"/>
       <c r="B24" s="92" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C24" s="93"/>
       <c r="D24" s="24" t="str">
@@ -3443,55 +2824,55 @@
       <c r="C25" s="93"/>
       <c r="D25" s="25">
         <f>$L$12</f>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="E25" s="25">
         <f t="shared" ref="E25:P25" si="1">$L$12</f>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F25" s="25">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G25" s="25">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="H25" s="25">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I25" s="25">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J25" s="25">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="K25" s="25">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="L25" s="25">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="M25" s="25">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="N25" s="25">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="O25" s="25">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="P25" s="25">
         <f t="shared" si="1"/>
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="Q25" s="4"/>
     </row>
@@ -3866,7 +3247,7 @@
       <c r="J44" s="4"/>
       <c r="K44" s="4"/>
       <c r="L44" s="62" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M44" s="62"/>
       <c r="N44" s="62"/>
@@ -3886,7 +3267,7 @@
       <c r="J45" s="4"/>
       <c r="K45" s="4"/>
       <c r="L45" s="52" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M45" s="52"/>
       <c r="N45" s="52"/>
